--- a/831-4-Rashincë-leg-bedri/3-Katet/regjistri/29-Koordinatat-e-kateve-831-4-Rashincë-leg-bedri.xlsx
+++ b/831-4-Rashincë-leg-bedri/3-Katet/regjistri/29-Koordinatat-e-kateve-831-4-Rashincë-leg-bedri.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shtime\MuzeQine\831-Muzeqine-legalizimi\831-9-Rashincë-legalizim\3-Katet\regjistri\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shtime\MuzeQine\831-Muzeqine-legalizimi\831-4-Rashincë-leg-bedri\3-Katet\regjistri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1D5A56-A7DD-4B6D-88C7-181D302C9197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98210CAF-71FC-45D0-8C52-41F069E7C37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="195" windowWidth="27795" windowHeight="16005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="255" windowWidth="28185" windowHeight="15945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$K$43</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="21">
   <si>
     <t>Y</t>
   </si>
@@ -80,6 +80,21 @@
   </si>
   <si>
     <t>perdhese</t>
+  </si>
+  <si>
+    <t>kati1</t>
+  </si>
+  <si>
+    <t>kati1-terasa</t>
+  </si>
+  <si>
+    <t>kati1-terase</t>
+  </si>
+  <si>
+    <t>Kati 1</t>
+  </si>
+  <si>
+    <t>Teras</t>
   </si>
 </sst>
 </file>
@@ -432,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -470,6 +485,42 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,44 +575,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -833,7 +857,7 @@
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>: 00831-2</a:t>
+            <a:t>: 00831-4</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1201,7 +1225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
@@ -1215,115 +1239,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36"/>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="2" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
     </row>
     <row r="4" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C8" s="37"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C9" s="40"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="42"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="43"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="45"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D12" s="4"/>
@@ -1361,158 +1385,254 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="11">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C15" s="5">
-        <v>7508008.2750000004</v>
+        <v>7507919.5442000004</v>
       </c>
       <c r="D15" s="5">
-        <v>4699807.9639999997</v>
+        <v>4699799.5301999999</v>
       </c>
       <c r="E15" s="10">
-        <v>599.678</v>
+        <v>598.42899999999997</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="H15" s="34" t="s">
+      <c r="H15" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="34">
-        <v>97.9</v>
+      <c r="I15" s="45">
+        <v>112.81</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" s="11">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C16" s="5">
-        <v>7508017.5080000004</v>
+        <v>7507917.7357000001</v>
       </c>
       <c r="D16" s="5">
-        <v>4699812.1720000003</v>
+        <v>4699799.3008000003</v>
       </c>
       <c r="E16" s="10">
-        <v>599.678</v>
+        <v>598.42899999999997</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="33"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="11">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="C17" s="5">
-        <v>7508013.5029999996</v>
+        <v>7507918.8229999999</v>
       </c>
       <c r="D17" s="5">
-        <v>4699820.9610000001</v>
+        <v>4699799.8277000003</v>
       </c>
       <c r="E17" s="10">
-        <v>599.678</v>
+        <v>598.42899999999997</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="33"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="C18" s="5">
-        <v>7508004.3159999996</v>
+        <v>7507919.8150000004</v>
       </c>
       <c r="D18" s="5">
-        <v>4699816.83</v>
+        <v>4699798.9649999999</v>
       </c>
       <c r="E18" s="10">
-        <v>599.678</v>
+        <v>598.31600000000003</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G18" s="33"/>
-      <c r="H18" s="14" t="s">
+      <c r="G18" s="26"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
+        <v>83</v>
+      </c>
+      <c r="C19" s="5">
+        <v>7507921.1739999996</v>
+      </c>
+      <c r="D19" s="5">
+        <v>4699796.0650000004</v>
+      </c>
+      <c r="E19" s="10">
+        <v>598.42899999999997</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="26"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
+        <v>84</v>
+      </c>
+      <c r="C20" s="5">
+        <v>7507921.4369999999</v>
+      </c>
+      <c r="D20" s="5">
+        <v>4699795.4979999997</v>
+      </c>
+      <c r="E20" s="10">
+        <v>598.27599999999995</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="26"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="11">
+        <v>85</v>
+      </c>
+      <c r="C21" s="5">
+        <v>7507921.216</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4699794.7510000002</v>
+      </c>
+      <c r="E21" s="10">
+        <v>598.26800000000003</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="26"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="11">
+        <v>86</v>
+      </c>
+      <c r="C22" s="5">
+        <v>7507920.159</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4699794.2589999996</v>
+      </c>
+      <c r="E22" s="10">
+        <v>598.28599999999994</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="26"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="11">
+        <v>87</v>
+      </c>
+      <c r="C23" s="5">
+        <v>7507921.6749999998</v>
+      </c>
+      <c r="D23" s="5">
+        <v>4699791.0080000004</v>
+      </c>
+      <c r="E23" s="10">
+        <v>598.27800000000002</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="26"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="11">
+        <v>88</v>
+      </c>
+      <c r="C24" s="5">
+        <v>7507907.9709999999</v>
+      </c>
+      <c r="D24" s="5">
+        <v>4699795.466</v>
+      </c>
+      <c r="E24" s="10">
+        <v>598.42899999999997</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="26"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="11">
+        <v>89</v>
+      </c>
+      <c r="C25" s="5">
+        <v>7507912.2120000003</v>
+      </c>
+      <c r="D25" s="5">
+        <v>4699786.5379999997</v>
+      </c>
+      <c r="E25" s="10">
+        <v>603.03700000000003</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="26"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="11">
+        <v>93</v>
+      </c>
+      <c r="C26" s="5">
+        <v>7507917.4340000004</v>
+      </c>
+      <c r="D26" s="5">
+        <v>4699799.9359999998</v>
+      </c>
+      <c r="E26" s="10">
+        <v>602.721</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="26"/>
+      <c r="H26" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I26" s="14">
         <f>SUM(I15:I17)</f>
-        <v>97.9</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D22" s="6"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D23" s="6"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D24" s="6"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D25" s="6"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D26" s="6"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
+        <v>112.81</v>
+      </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D27" s="6"/>
@@ -1523,114 +1643,336 @@
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D28" s="6"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+      <c r="B28" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D29" s="6"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="B29" s="11">
+        <v>60</v>
+      </c>
+      <c r="C29" s="5">
+        <v>7507907.9709999999</v>
+      </c>
+      <c r="D29" s="5">
+        <v>4699795.466</v>
+      </c>
+      <c r="E29" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="I29" s="47">
+        <v>103.443</v>
+      </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D30" s="6"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
+      <c r="B30" s="11">
+        <v>90</v>
+      </c>
+      <c r="C30" s="5">
+        <v>7507912.2120000003</v>
+      </c>
+      <c r="D30" s="5">
+        <v>4699786.5379999997</v>
+      </c>
+      <c r="E30" s="10">
+        <v>603.03700000000003</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="26"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D31" s="6"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
+      <c r="B31" s="11">
+        <v>91</v>
+      </c>
+      <c r="C31" s="5">
+        <v>7507921.6749999998</v>
+      </c>
+      <c r="D31" s="5">
+        <v>4699791.0080000004</v>
+      </c>
+      <c r="E31" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G31" s="26"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D32" s="6"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
+      <c r="B32" s="11">
+        <v>92</v>
+      </c>
+      <c r="C32" s="5">
+        <v>7507917.4340000004</v>
+      </c>
+      <c r="D32" s="5">
+        <v>4699799.9359999998</v>
+      </c>
+      <c r="E32" s="10">
+        <v>602.721</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="26"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D33" s="6"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-    </row>
-    <row r="34" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K34" s="1"/>
-    </row>
-    <row r="35" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="B33" s="11">
+        <v>66</v>
+      </c>
+      <c r="C33" s="5">
+        <v>7507919.5442000004</v>
+      </c>
+      <c r="D33" s="5">
+        <v>4699799.5301999999</v>
+      </c>
+      <c r="E33" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="26"/>
+      <c r="H33" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="15">
+        <v>9.3670000000000009</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="11">
+        <v>98</v>
+      </c>
+      <c r="C34" s="5">
+        <v>7507919.8150000004</v>
+      </c>
+      <c r="D34" s="5">
+        <v>4699798.9649999999</v>
+      </c>
+      <c r="E34" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="26"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="11">
+        <v>99</v>
+      </c>
+      <c r="C35" s="5">
+        <v>7507921.4409999996</v>
+      </c>
+      <c r="D35" s="5">
+        <v>4699795.4979999997</v>
+      </c>
+      <c r="E35" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="26"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="11">
+        <v>100</v>
+      </c>
+      <c r="C36" s="5">
+        <v>7507921.216</v>
+      </c>
+      <c r="D36" s="5">
+        <v>4699794.7510000002</v>
+      </c>
+      <c r="E36" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="26"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="11">
+        <v>101</v>
+      </c>
+      <c r="C37" s="5">
+        <v>7507920.1358000003</v>
+      </c>
+      <c r="D37" s="5">
+        <v>4699794.2482000003</v>
+      </c>
+      <c r="E37" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="26"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="11">
+        <v>25</v>
+      </c>
+      <c r="C38" s="5">
+        <v>7507918.8229999999</v>
+      </c>
+      <c r="D38" s="5">
+        <v>4699799.8277000003</v>
+      </c>
+      <c r="E38" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="26"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="11">
+        <v>28</v>
+      </c>
+      <c r="C39" s="5">
+        <v>7507917.7357000001</v>
+      </c>
+      <c r="D39" s="5">
+        <v>4699799.3008000003</v>
+      </c>
+      <c r="E39" s="10">
+        <v>602.04</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="26"/>
+      <c r="H39" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I39" s="14">
+        <f>SUM(I29:I33)</f>
+        <v>112.81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D40" s="6"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+    </row>
+    <row r="41" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K41" s="1"/>
+    </row>
+    <row r="42" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="24" t="s">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="F35" s="25"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="20" t="s">
+      <c r="F42" s="37"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="I35" s="21"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="16"/>
-    </row>
-    <row r="36" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="27" t="s">
+      <c r="I42" s="33"/>
+      <c r="J42" s="27"/>
+      <c r="K42" s="28"/>
+    </row>
+    <row r="43" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="30">
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="42">
         <v>140</v>
       </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="18"/>
-    </row>
-    <row r="37" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="K37" s="1"/>
-    </row>
-    <row r="38" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="K38" s="1"/>
-    </row>
-    <row r="39" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="K39" s="1"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="30"/>
+    </row>
+    <row r="44" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K44" s="1"/>
+    </row>
+    <row r="45" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K45" s="1"/>
+    </row>
+    <row r="46" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="K46" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="C8:J10"/>
-    <mergeCell ref="G15:G18"/>
-    <mergeCell ref="J35:K36"/>
+    <mergeCell ref="G15:G26"/>
+    <mergeCell ref="J42:K43"/>
     <mergeCell ref="A3:K6"/>
-    <mergeCell ref="H35:I36"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H42:I43"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="E43:G43"/>
     <mergeCell ref="H15:H17"/>
     <mergeCell ref="I15:I17"/>
+    <mergeCell ref="G29:G39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="58" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
